--- a/docs/01_設計/12_エラー設計書.xlsx
+++ b/docs/01_設計/12_エラー設計書.xlsx
@@ -763,27 +763,27 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>対象なし / 未認証</t>
+          <t>対象なし / 未認証 / 権限不足</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>404 / 401</t>
+          <t>404 / 401 / 403</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>RES-TASK-404 / AUTH-001</t>
+          <t>RES-TASK-404 / AUTH-001 / AUTH-005</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>削除済みなど</t>
+          <t>削除済み、他人データ、権限対象外</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>一覧へ戻す</t>
+          <t>権限エラー表示 / 一覧へ戻す</t>
         </is>
       </c>
     </row>

--- a/docs/01_設計/12_エラー設計書.xlsx
+++ b/docs/01_設計/12_エラー設計書.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/apple/Documents/projects/task-manager-app/docs/01_設計/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D6A562-9142-1443-9C7C-3C8834C5914A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C48508-BA09-E144-BB34-701402CE217C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19440" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="19440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="概要" sheetId="1" r:id="rId1"/>
+    <sheet name="概要" sheetId="12" r:id="rId1"/>
     <sheet name="基本方針" sheetId="2" r:id="rId2"/>
     <sheet name="レスポンス形式" sheetId="3" r:id="rId3"/>
     <sheet name="HTTPステータス" sheetId="4" r:id="rId4"/>
@@ -25,6 +25,9 @@
     <sheet name="API別代表エラー" sheetId="10" r:id="rId10"/>
     <sheet name="設計意図" sheetId="11" r:id="rId11"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">機能別エラーコード!$A$2:$G$18</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -43,10 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="573" uniqueCount="380">
-  <si>
-    <t>エラー設計書（機能別強化版）</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="321">
   <si>
     <t>項目</t>
   </si>
@@ -69,9 +69,6 @@
     <t>強化ポイント</t>
   </si>
   <si>
-    <t>機能別エラーコードを定義し、認証、タスク、コメント、添付、チーム、メンバー、システムで分類する。</t>
-  </si>
-  <si>
     <t>関連成果物</t>
   </si>
   <si>
@@ -105,9 +102,6 @@
     <t>ユーザー向け通知と障害調査を分離するため</t>
   </si>
   <si>
-    <t>ControllerAdviceで例外ごとにマッピング</t>
-  </si>
-  <si>
     <t>表現</t>
   </si>
   <si>
@@ -117,24 +111,9 @@
     <t>フロント・ログ・運用で共通言語化するため</t>
   </si>
   <si>
-    <t>レスポンス形式を統一</t>
-  </si>
-  <si>
     <t>追跡性</t>
   </si>
   <si>
-    <t>requestId を全エラーで返却</t>
-  </si>
-  <si>
-    <t>ログとAPIレスポンスを紐づけるため</t>
-  </si>
-  <si>
-    <t>MDC等を利用</t>
-  </si>
-  <si>
-    <t>CloudWatch連携</t>
-  </si>
-  <si>
     <t>セキュリティ</t>
   </si>
   <si>
@@ -144,9 +123,6 @@
     <t>攻撃者に余計な情報を与えないため</t>
   </si>
   <si>
-    <t>認証失敗メッセージは抽象化</t>
-  </si>
-  <si>
     <t>入力エラー</t>
   </si>
   <si>
@@ -234,9 +210,6 @@
     <t>項目別詳細</t>
   </si>
   <si>
-    <t>[{"field":"title","message":"タイトルは必須です"}]</t>
-  </si>
-  <si>
     <t>フォームエラー表示</t>
   </si>
   <si>
@@ -261,9 +234,6 @@
     <t>相関ID</t>
   </si>
   <si>
-    <t>req-20260403-0001</t>
-  </si>
-  <si>
     <t>ログ追跡</t>
   </si>
   <si>
@@ -297,9 +267,6 @@
     <t>未認証</t>
   </si>
   <si>
-    <t>JWTなし、JWT不正、期限切れ</t>
-  </si>
-  <si>
     <t>認証エラー</t>
   </si>
   <si>
@@ -309,9 +276,6 @@
     <t>権限不足</t>
   </si>
   <si>
-    <t>他人のタスク更新、管理者権限不足</t>
-  </si>
-  <si>
     <t>認可エラー</t>
   </si>
   <si>
@@ -321,27 +285,18 @@
     <t>対象なし</t>
   </si>
   <si>
-    <t>タスク不存在、コメント不存在</t>
-  </si>
-  <si>
     <t>409 Conflict</t>
   </si>
   <si>
     <t>状態競合・重複</t>
   </si>
   <si>
-    <t>メール重複、メンバー既存在</t>
-  </si>
-  <si>
     <t>500 Internal Server Error</t>
   </si>
   <si>
     <t>システム障害</t>
   </si>
   <si>
-    <t>DB障害、S3障害、想定外例外</t>
-  </si>
-  <si>
     <t>システムエラー</t>
   </si>
   <si>
@@ -363,48 +318,24 @@
     <t>認証</t>
   </si>
   <si>
-    <t>AUTH-001</t>
-  </si>
-  <si>
     <t>401</t>
   </si>
   <si>
-    <t>ログイン画面へ遷移</t>
-  </si>
-  <si>
-    <t>AUTH-002</t>
-  </si>
-  <si>
     <t>認証失敗</t>
   </si>
   <si>
-    <t>「認証に失敗しました」を表示</t>
-  </si>
-  <si>
-    <t>AUTH-003</t>
-  </si>
-  <si>
     <t>トークン不正</t>
   </si>
   <si>
     <t>再ログイン要求</t>
   </si>
   <si>
-    <t>AUTH-004</t>
-  </si>
-  <si>
     <t>トークン期限切れ</t>
   </si>
   <si>
     <t>認可</t>
   </si>
   <si>
-    <t>AUTH-005</t>
-  </si>
-  <si>
-    <t>アクセス権限なし</t>
-  </si>
-  <si>
     <t>403</t>
   </si>
   <si>
@@ -414,9 +345,6 @@
     <t>ユーザー</t>
   </si>
   <si>
-    <t>USR-001</t>
-  </si>
-  <si>
     <t>メール重複</t>
   </si>
   <si>
@@ -429,9 +357,6 @@
     <t>新規登録</t>
   </si>
   <si>
-    <t>USR-002</t>
-  </si>
-  <si>
     <t>ユーザー不存在</t>
   </si>
   <si>
@@ -441,39 +366,18 @@
     <t>担当者選択エラー表示</t>
   </si>
   <si>
-    <t>USR-003</t>
-  </si>
-  <si>
-    <t>パスワード不正</t>
-  </si>
-  <si>
-    <t>入力エラー表示</t>
-  </si>
-  <si>
     <t>タスク</t>
   </si>
   <si>
-    <t>タイトル未入力</t>
-  </si>
-  <si>
     <t>title項目にエラー表示</t>
   </si>
   <si>
-    <t>VAL-TASK-002</t>
-  </si>
-  <si>
     <t>ステータス不正</t>
   </si>
   <si>
     <t>status項目にエラー表示</t>
   </si>
   <si>
-    <t>VAL-TASK-003</t>
-  </si>
-  <si>
-    <t>期限不正</t>
-  </si>
-  <si>
     <t>dueDate項目にエラー表示</t>
   </si>
   <si>
@@ -483,183 +387,18 @@
     <t>タスク不存在</t>
   </si>
   <si>
-    <t>一覧へ戻す/再読込</t>
-  </si>
-  <si>
-    <t>PERM-TASK-403-UPD</t>
-  </si>
-  <si>
     <t>更新権限なし</t>
   </si>
   <si>
-    <t>PERM-TASK-403-DEL</t>
-  </si>
-  <si>
     <t>削除権限なし</t>
   </si>
   <si>
-    <t>コメント</t>
-  </si>
-  <si>
-    <t>VAL-COMM-001</t>
-  </si>
-  <si>
-    <t>コメント未入力</t>
-  </si>
-  <si>
-    <t>content項目にエラー表示</t>
-  </si>
-  <si>
-    <t>RES-COMM-404</t>
-  </si>
-  <si>
-    <t>コメント不存在</t>
-  </si>
-  <si>
-    <t>一覧再取得</t>
-  </si>
-  <si>
-    <t>PERM-COMM-403-UPD</t>
-  </si>
-  <si>
-    <t>編集権限なし</t>
-  </si>
-  <si>
-    <t>PERM-COMM-403-DEL</t>
-  </si>
-  <si>
-    <t>添付</t>
-  </si>
-  <si>
-    <t>VAL-FILE-001</t>
-  </si>
-  <si>
-    <t>ファイル未選択</t>
-  </si>
-  <si>
-    <t>ファイル選択エラー表示</t>
-  </si>
-  <si>
-    <t>VAL-FILE-002</t>
-  </si>
-  <si>
-    <t>サイズ超過</t>
-  </si>
-  <si>
-    <t>サイズ超過表示</t>
-  </si>
-  <si>
-    <t>VAL-FILE-003</t>
-  </si>
-  <si>
-    <t>拡張子不正</t>
-  </si>
-  <si>
-    <t>形式不正表示</t>
-  </si>
-  <si>
-    <t>RES-FILE-404</t>
-  </si>
-  <si>
-    <t>添付不存在</t>
-  </si>
-  <si>
-    <t>SYS-S3-001</t>
-  </si>
-  <si>
-    <t>アップロード失敗</t>
-  </si>
-  <si>
     <t>500</t>
   </si>
   <si>
-    <t>再試行案内</t>
-  </si>
-  <si>
-    <t>SYS-S3-002</t>
-  </si>
-  <si>
-    <t>ダウンロード失敗</t>
-  </si>
-  <si>
-    <t>チーム</t>
-  </si>
-  <si>
-    <t>VAL-TEAM-001</t>
-  </si>
-  <si>
-    <t>チーム名未入力</t>
-  </si>
-  <si>
-    <t>name項目にエラー表示</t>
-  </si>
-  <si>
-    <t>RES-TEAM-404</t>
-  </si>
-  <si>
-    <t>チーム不存在</t>
-  </si>
-  <si>
-    <t>一覧へ戻す</t>
-  </si>
-  <si>
-    <t>PERM-TEAM-403</t>
-  </si>
-  <si>
-    <t>権限なし</t>
-  </si>
-  <si>
-    <t>PERM-TEAM-403-ADMIN</t>
-  </si>
-  <si>
-    <t>管理者権限必要</t>
-  </si>
-  <si>
-    <t>管理者のみ表示</t>
-  </si>
-  <si>
-    <t>メンバー</t>
-  </si>
-  <si>
-    <t>MEM-001</t>
-  </si>
-  <si>
-    <t>メンバー既存在</t>
-  </si>
-  <si>
-    <t>重複追加エラー表示</t>
-  </si>
-  <si>
-    <t>MEM-002</t>
-  </si>
-  <si>
-    <t>対象ユーザー不存在</t>
-  </si>
-  <si>
-    <t>ユーザー選択エラー表示</t>
-  </si>
-  <si>
-    <t>MEM-403</t>
-  </si>
-  <si>
-    <t>管理者権限なし</t>
-  </si>
-  <si>
     <t>システム</t>
   </si>
   <si>
-    <t>SYS-DB-001</t>
-  </si>
-  <si>
-    <t>DB接続失敗</t>
-  </si>
-  <si>
-    <t>汎用エラー画面/メッセージ</t>
-  </si>
-  <si>
-    <t>SYS-999</t>
-  </si>
-  <si>
     <t>想定外例外</t>
   </si>
   <si>
@@ -699,9 +438,6 @@
     <t>複数項目エラーをまとめて返す</t>
   </si>
   <si>
-    <t>title/dueDate等</t>
-  </si>
-  <si>
     <t>まとめて表示可能</t>
   </si>
   <si>
@@ -723,78 +459,18 @@
     <t>ハンドリング方針</t>
   </si>
   <si>
-    <t>ValidationException</t>
-  </si>
-  <si>
-    <t>VAL-XXX-001</t>
-  </si>
-  <si>
-    <t>details付きで返却</t>
-  </si>
-  <si>
-    <t>AuthenticationException</t>
-  </si>
-  <si>
-    <t>認証失敗として返却</t>
-  </si>
-  <si>
     <t>詳細を出しすぎない</t>
   </si>
   <si>
-    <t>AccessDeniedException</t>
-  </si>
-  <si>
-    <t>AUTH-005 / PERM-XXX-403</t>
-  </si>
-  <si>
-    <t>権限不足として返却</t>
-  </si>
-  <si>
-    <t>NotFoundException</t>
-  </si>
-  <si>
-    <t>RES-XXX-404</t>
-  </si>
-  <si>
     <t>対象なしとして返却</t>
   </si>
   <si>
     <t>ConflictException</t>
   </si>
   <si>
-    <t>USR-001 / MEM-001</t>
-  </si>
-  <si>
-    <t>重複・競合として返却</t>
-  </si>
-  <si>
-    <t>StorageException</t>
-  </si>
-  <si>
-    <t>外部サービスエラーとして返却</t>
-  </si>
-  <si>
     <t>ERROR</t>
   </si>
   <si>
-    <t>S3など</t>
-  </si>
-  <si>
-    <t>DataAccessException</t>
-  </si>
-  <si>
-    <t>DBエラーとして返却</t>
-  </si>
-  <si>
-    <t>Exception</t>
-  </si>
-  <si>
-    <t>汎用システムエラーとして返却</t>
-  </si>
-  <si>
-    <t>ControllerAdviceで一元管理</t>
-  </si>
-  <si>
     <t>ログ設計との連携</t>
   </si>
   <si>
@@ -804,57 +480,12 @@
     <t>requestId連携</t>
   </si>
   <si>
-    <t>レスポンスのrequestIdとログのrequestIdを一致させる</t>
-  </si>
-  <si>
-    <t>全レベル</t>
-  </si>
-  <si>
-    <t>全ログ</t>
-  </si>
-  <si>
-    <t>障害調査の起点</t>
-  </si>
-  <si>
     <t>errorCode連携</t>
   </si>
   <si>
-    <t>errorCodeをログにも出力する</t>
-  </si>
-  <si>
-    <t>WARN/ERROR</t>
-  </si>
-  <si>
-    <t>業務/例外</t>
-  </si>
-  <si>
-    <t>検索性向上</t>
-  </si>
-  <si>
-    <t>業務エラーは WARN で出力</t>
-  </si>
-  <si>
     <t>権限不足、対象なし</t>
   </si>
   <si>
-    <t>アプリログ</t>
-  </si>
-  <si>
-    <t>システムエラーは ERROR で出力</t>
-  </si>
-  <si>
-    <t>DB障害、S3障害</t>
-  </si>
-  <si>
-    <t>例外ログ</t>
-  </si>
-  <si>
-    <t>ログイン失敗やJWT不正は WARN</t>
-  </si>
-  <si>
-    <t>認証ログ</t>
-  </si>
-  <si>
     <t>セキュリティ上のメッセージ方針</t>
   </si>
   <si>
@@ -879,21 +510,9 @@
     <t>認証情報の推測を防ぐ</t>
   </si>
   <si>
-    <t>このチームの管理者ではないため変更できません</t>
-  </si>
-  <si>
-    <t>操作権限がありません</t>
-  </si>
-  <si>
-    <t>内部ルールを出しすぎない</t>
-  </si>
-  <si>
     <t>DB接続タイムアウト</t>
   </si>
   <si>
-    <t>システムエラーが発生しました</t>
-  </si>
-  <si>
     <t>内部構成を秘匿する</t>
   </si>
   <si>
@@ -903,9 +522,6 @@
     <t>JWT署名が不正です</t>
   </si>
   <si>
-    <t>認証情報が無効です</t>
-  </si>
-  <si>
     <t>内部実装を露出しない</t>
   </si>
   <si>
@@ -927,63 +543,24 @@
     <t>POST /api/auth/register</t>
   </si>
   <si>
-    <t>メール重複 / 入力不正</t>
-  </si>
-  <si>
-    <t>409 / 400</t>
-  </si>
-  <si>
-    <t>USR-001 / VAL-USR-001</t>
-  </si>
-  <si>
-    <t>メール重複、必須不足</t>
-  </si>
-  <si>
-    <t>項目エラー表示</t>
-  </si>
-  <si>
     <t>ログイン</t>
   </si>
   <si>
     <t>POST /api/auth/login</t>
   </si>
   <si>
-    <t>メール/パスワード不一致</t>
-  </si>
-  <si>
-    <t>認証失敗メッセージ</t>
-  </si>
-  <si>
     <t>タスク一覧取得</t>
   </si>
   <si>
     <t>GET /api/tasks</t>
   </si>
   <si>
-    <t>JWTなし</t>
-  </si>
-  <si>
-    <t>ログイン画面へ</t>
-  </si>
-  <si>
     <t>タスク詳細取得</t>
   </si>
   <si>
     <t>GET /api/tasks/{id}</t>
   </si>
   <si>
-    <t>対象なし / 未認証 / 権限不足</t>
-  </si>
-  <si>
-    <t>404 / 401 / 403</t>
-  </si>
-  <si>
-    <t>RES-TASK-404 / AUTH-001 / AUTH-005</t>
-  </si>
-  <si>
-    <t>削除済み、他人データ、権限対象外</t>
-  </si>
-  <si>
     <t>権限エラー表示 / 一覧へ戻す</t>
   </si>
   <si>
@@ -993,174 +570,27 @@
     <t>POST /api/tasks</t>
   </si>
   <si>
-    <t>入力不正 / 未認証</t>
-  </si>
-  <si>
     <t>400 / 401</t>
   </si>
   <si>
-    <t>VAL-TASK-001 / AUTH-001</t>
-  </si>
-  <si>
-    <t>必須不足、JWTなし</t>
-  </si>
-  <si>
     <t>タスク更新</t>
   </si>
   <si>
     <t>PUT /api/tasks/{id}</t>
   </si>
   <si>
-    <t>対象なし / 権限不足 / 入力不正</t>
-  </si>
-  <si>
-    <t>404 / 403 / 400</t>
-  </si>
-  <si>
-    <t>RES-TASK-404 / PERM-TASK-403-UPD / VAL-TASK-002</t>
-  </si>
-  <si>
-    <t>対象なし、他人データ</t>
-  </si>
-  <si>
-    <t>権限エラー/再読込</t>
-  </si>
-  <si>
     <t>タスク削除</t>
   </si>
   <si>
     <t>DELETE /api/tasks/{id}</t>
   </si>
   <si>
-    <t>対象なし / 権限不足</t>
-  </si>
-  <si>
-    <t>404 / 403</t>
-  </si>
-  <si>
-    <t>RES-TASK-404 / PERM-TASK-403-DEL</t>
-  </si>
-  <si>
-    <t>削除済み、他人データ</t>
-  </si>
-  <si>
-    <t>コメント投稿</t>
-  </si>
-  <si>
-    <t>POST /api/tasks/{id}/comments</t>
-  </si>
-  <si>
-    <t>入力不正 / 対象なし</t>
-  </si>
-  <si>
-    <t>400 / 404</t>
-  </si>
-  <si>
-    <t>VAL-COMM-001 / RES-TASK-404</t>
-  </si>
-  <si>
-    <t>空コメント、タスク不存在</t>
-  </si>
-  <si>
-    <t>コメント更新</t>
-  </si>
-  <si>
-    <t>PUT /api/comments/{id}</t>
-  </si>
-  <si>
-    <t>RES-COMM-404 / PERM-COMM-403-UPD</t>
-  </si>
-  <si>
-    <t>他人コメント</t>
-  </si>
-  <si>
-    <t>コメント削除</t>
-  </si>
-  <si>
-    <t>DELETE /api/comments/{id}</t>
-  </si>
-  <si>
-    <t>RES-COMM-404 / PERM-COMM-403-DEL</t>
-  </si>
-  <si>
-    <t>削除済み等</t>
-  </si>
-  <si>
-    <t>添付アップロード</t>
-  </si>
-  <si>
-    <t>POST /api/tasks/{id}/attachments</t>
-  </si>
-  <si>
-    <t>未選択 / サイズ超過 / S3障害</t>
-  </si>
-  <si>
-    <t>400 / 500</t>
-  </si>
-  <si>
-    <t>VAL-FILE-001 / VAL-FILE-002 / SYS-S3-001</t>
-  </si>
-  <si>
-    <t>選択なし、S3失敗</t>
-  </si>
-  <si>
-    <t>添付ダウンロード</t>
-  </si>
-  <si>
-    <t>GET /api/attachments/{id}/download</t>
-  </si>
-  <si>
-    <t>対象なし / S3障害</t>
-  </si>
-  <si>
-    <t>404 / 500</t>
-  </si>
-  <si>
-    <t>RES-FILE-404 / SYS-S3-002</t>
-  </si>
-  <si>
-    <t>削除済み、S3失敗</t>
-  </si>
-  <si>
-    <t>チーム作成</t>
-  </si>
-  <si>
-    <t>POST /api/teams</t>
-  </si>
-  <si>
-    <t>VAL-TEAM-001 / AUTH-001</t>
-  </si>
-  <si>
-    <t>必須不足</t>
-  </si>
-  <si>
-    <t>メンバー追加</t>
-  </si>
-  <si>
-    <t>POST /api/teams/{id}/members</t>
-  </si>
-  <si>
-    <t>権限不足 / 重複 / 対象なし</t>
-  </si>
-  <si>
-    <t>403 / 409 / 404</t>
-  </si>
-  <si>
-    <t>MEM-403 / MEM-001 / MEM-002</t>
-  </si>
-  <si>
-    <t>管理者以外、既追加</t>
-  </si>
-  <si>
     <t>エラー設計の設計意図</t>
   </si>
   <si>
     <t>設計意図</t>
   </si>
   <si>
-    <t>機能単位でエラーコードを分離し、フロントエンドでの分岐、運用時の調査、ログ検索をしやすくした。</t>
-  </si>
-  <si>
     <t>ユーザー体験</t>
   </si>
   <si>
@@ -1170,20 +600,436 @@
     <t>運用性</t>
   </si>
   <si>
-    <t>requestId + errorCode で CloudWatch Logs と突合できるようにし、障害調査を容易にした。</t>
-  </si>
-  <si>
     <t>認証失敗やシステム障害では内部情報を出しすぎず、安全なメッセージに統一した。</t>
   </si>
   <si>
     <t>面接での説明ポイント</t>
   </si>
   <si>
-    <t>業務エラーとシステムエラーの分離、機能別エラーコード設計、バリデーションdetails、ControllerAdviceによる例外一元管理、CloudWatchとの連携を説明できる。</t>
-  </si>
-  <si>
-    <t>・詳細は出しすぎない
-・画面遷移しない</t>
+    <t>CustomAuthenticationEntryPoint / GlobalExceptionHandler で統一</t>
+  </si>
+  <si>
+    <t>ErrorResponse(timestamp,status,errorCode,message,details,path,requestId)</t>
+  </si>
+  <si>
+    <t>requestId を全エラーで返却し、レスポンスヘッダにも設定する</t>
+  </si>
+  <si>
+    <t>フロントと障害調査で同一 ID を参照するため</t>
+  </si>
+  <si>
+    <t>RequestIdFilter が X-Request-Id を採番し request 属性と response header に設定</t>
+  </si>
+  <si>
+    <t>アプリログ連携は未実装</t>
+  </si>
+  <si>
+    <t>認証エラーは抽象化し、権限エラーはコード別メッセージで返却</t>
+  </si>
+  <si>
+    <t>[{"field":"title","message":"タイトルを入力してください"}]</t>
+  </si>
+  <si>
+    <t>550e8400-e29b-41d4-a716-446655440000</t>
+  </si>
+  <si>
+    <t>未認証 / 認証失敗</t>
+  </si>
+  <si>
+    <t>JWTなし、JWT不正、期限切れ、ログイン失敗</t>
+  </si>
+  <si>
+    <t>他人タスクの参照 / 更新 / 削除</t>
+  </si>
+  <si>
+    <t>タスク不存在、assignedUserId不存在</t>
+  </si>
+  <si>
+    <t>DB障害、想定外例外</t>
+  </si>
+  <si>
+    <t>401時はtoken破棄・/loginへ</t>
+  </si>
+  <si>
+    <t>ログイン画面でエラー表示</t>
+  </si>
+  <si>
+    <t>BadCredentialsException</t>
+  </si>
+  <si>
+    <t>署名不正・形式不正</t>
+  </si>
+  <si>
+    <t>ExpiredJwtException</t>
+  </si>
+  <si>
+    <t>タスク詳細参照</t>
+  </si>
+  <si>
+    <t>参照権限なし</t>
+  </si>
+  <si>
+    <t>message は「対象タスクの参照権限がありません」</t>
+  </si>
+  <si>
+    <t>入力</t>
+  </si>
+  <si>
+    <t>共通入力</t>
+  </si>
+  <si>
+    <t>入力内容不正</t>
+  </si>
+  <si>
+    <t>details を各項目へ表示</t>
+  </si>
+  <si>
+    <t>登録 / ログイン / priority不正 等</t>
+  </si>
+  <si>
+    <t>タイトル不正</t>
+  </si>
+  <si>
+    <t>期限形式不正</t>
+  </si>
+  <si>
+    <t>assignedUserId / currentUser 解決失敗</t>
+  </si>
+  <si>
+    <t>一覧へ戻す / 再読込</t>
+  </si>
+  <si>
+    <t>DBアクセス失敗</t>
+  </si>
+  <si>
+    <t>汎用エラーメッセージ表示</t>
+  </si>
+  <si>
+    <t>title / status / dueDate / priority / name / email / password</t>
+  </si>
+  <si>
+    <t>MethodArgumentNotValidException</t>
+  </si>
+  <si>
+    <t>Bean Validation の field errors を details 付きで返却</t>
+  </si>
+  <si>
+    <t>DTO検証</t>
+  </si>
+  <si>
+    <t>HttpMessageNotReadableException</t>
+  </si>
+  <si>
+    <t>enum不正・日付形式不正を項目エラーへ補正</t>
+  </si>
+  <si>
+    <t>priority 不正もここで補正</t>
+  </si>
+  <si>
+    <t>ログイン失敗として返却</t>
+  </si>
+  <si>
+    <t>AuthenticationEntryPoint</t>
+  </si>
+  <si>
+    <t>AUTH-001 / AUTH-003 / AUTH-004</t>
+  </si>
+  <si>
+    <t>未認証、JWT不正、期限切れを JSON で返却</t>
+  </si>
+  <si>
+    <t>JwtAuthenticationFilter から委譲</t>
+  </si>
+  <si>
+    <t>ResourceNotFoundException</t>
+  </si>
+  <si>
+    <t>重複エラーとして返却</t>
+  </si>
+  <si>
+    <t>BusinessException / AccessDeniedException</t>
+  </si>
+  <si>
+    <t>権限エラーとして返却</t>
+  </si>
+  <si>
+    <t>業務ルール違反 / Spring Security</t>
+  </si>
+  <si>
+    <t>DataAccessException / Exception</t>
+  </si>
+  <si>
+    <t>DBエラーと想定外例外を汎用エラーとして返却</t>
+  </si>
+  <si>
+    <t>ControllerAdvice で一元管理</t>
+  </si>
+  <si>
+    <t>RequestIdFilter が requestId を生成し、レスポンスヘッダ X-Request-Id に設定する</t>
+  </si>
+  <si>
+    <t>全エラー</t>
+  </si>
+  <si>
+    <t>APIレスポンス</t>
+  </si>
+  <si>
+    <t>アプリログへの出力は未実装</t>
+  </si>
+  <si>
+    <t>errorCode をレスポンス本文に含める</t>
+  </si>
+  <si>
+    <t>ログ出力との突合は今後の拡張</t>
+  </si>
+  <si>
+    <t>フロントは code / status / details で分岐する</t>
+  </si>
+  <si>
+    <t>4xx</t>
+  </si>
+  <si>
+    <t>フロント制御</t>
+  </si>
+  <si>
+    <t>バックエンドのログレベル出力は未実装</t>
+  </si>
+  <si>
+    <t>message は汎用文言に統一する</t>
+  </si>
+  <si>
+    <t>5xx</t>
+  </si>
+  <si>
+    <t>詳細はサーバ側例外で保持</t>
+  </si>
+  <si>
+    <t>401 時はフロントが token を破棄し /login へ遷移する</t>
+  </si>
+  <si>
+    <t>UNAUTHORIZED_EVENT を発火</t>
+  </si>
+  <si>
+    <t>他人タスクは更新できません</t>
+  </si>
+  <si>
+    <t>対象タスクの参照権限がありません / タスク更新権限がありません / タスク削除権限がありません</t>
+  </si>
+  <si>
+    <t>操作可否だけを伝え、内部ルールを出しすぎない</t>
+  </si>
+  <si>
+    <t>システムエラーが発生しました。しばらくしてから再度お試しください。</t>
+  </si>
+  <si>
+    <t>トークンが不正です / セッションの有効期限が切れています</t>
+  </si>
+  <si>
+    <t>入力不正 / メール重複</t>
+  </si>
+  <si>
+    <t>400 / 409</t>
+  </si>
+  <si>
+    <t>必須不足、形式不正、重複メール</t>
+  </si>
+  <si>
+    <t>details を項目表示 / 重複メッセージ表示</t>
+  </si>
+  <si>
+    <t>入力不正 / 認証失敗</t>
+  </si>
+  <si>
+    <t>必須不足、形式不正、メール/パスワード不一致</t>
+  </si>
+  <si>
+    <t>項目エラーまたは認証失敗メッセージ</t>
+  </si>
+  <si>
+    <t>認証確認</t>
+  </si>
+  <si>
+    <t>GET /api/auth-test/me</t>
+  </si>
+  <si>
+    <t>未認証 / JWT不正 / 期限切れ</t>
+  </si>
+  <si>
+    <t>Authorization なし、不正トークン、期限切れ</t>
+  </si>
+  <si>
+    <t>token破棄・/loginへ</t>
+  </si>
+  <si>
+    <t>保護APIへの未認証アクセス</t>
+  </si>
+  <si>
+    <t>対象なし / 権限不足 / 未認証</t>
+  </si>
+  <si>
+    <t>404 / 403 / 401</t>
+  </si>
+  <si>
+    <t>taskId不存在、他人タスク、JWTなし等</t>
+  </si>
+  <si>
+    <t>入力不正 / 担当者不存在 / 未認証</t>
+  </si>
+  <si>
+    <t>400 / 404 / 401</t>
+  </si>
+  <si>
+    <t>入力不正、assignedUserId不存在、JWTなし</t>
+  </si>
+  <si>
+    <t>項目エラー表示 / token破棄</t>
+  </si>
+  <si>
+    <t>入力不正 / 対象なし / 権限不足 / 未認証</t>
+  </si>
+  <si>
+    <t>400 / 404 / 403 / 401</t>
+  </si>
+  <si>
+    <t>入力不正、taskId不存在、作成者/担当者以外</t>
+  </si>
+  <si>
+    <t>項目エラー / 権限エラー表示</t>
+  </si>
+  <si>
+    <t>削除済み、作成者以外、JWTなし等</t>
+  </si>
+  <si>
+    <t>一覧へ戻す / 権限エラー表示</t>
+  </si>
+  <si>
+    <t>ユーザー一覧</t>
+  </si>
+  <si>
+    <t>GET /api/users</t>
+  </si>
+  <si>
+    <t>現行実装で利用するエラーコードだけに絞り、フロントエンドが code / status / details で分岐できるようにした。</t>
+  </si>
+  <si>
+    <t>requestId をレスポンスへ返す実装まで完了。アプリログとの突合は今後の拡張ポイント。</t>
+  </si>
+  <si>
+    <t>ControllerAdvice、AuthenticationEntryPoint、AccessDeniedHandler、RequestIdFilter による一元化を説明できる。</t>
+  </si>
+  <si>
+    <t>機能別エラーコードを定義し、認証、入力、ユーザー、タスク、システムで分類する。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ERR-AUTH-001</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ERR-AUTH-002</t>
+  </si>
+  <si>
+    <t>ERR-AUTH-002</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ERR-AUTH-003</t>
+  </si>
+  <si>
+    <t>ERR-AUTH-004</t>
+  </si>
+  <si>
+    <t>ERR-TASK-001</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ERR-TASK-002</t>
+  </si>
+  <si>
+    <t>ERR-TASK-003</t>
+  </si>
+  <si>
+    <t>ERR-TASK-004</t>
+  </si>
+  <si>
+    <t>ERR-TASK-005</t>
+  </si>
+  <si>
+    <t>ERR-TASK-006</t>
+  </si>
+  <si>
+    <t>ERR-SYS-001</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ERR-SYS-999</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ERR-AUTH-005</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ERR-USR-001</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ERR-USR-002</t>
+  </si>
+  <si>
+    <t>エラー設計書</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ERR-INPUT-001</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ERR-INPUT-001 / ERR-TASK-001-003</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ERR-INPUT-001 / ERR-TASK-002 / ERR-TASK-003</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ERR-AUTH-001 / ERR-AUTH-003 / ERR-AUTH-004</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ERR-USR-002 / ERR-TASK-004</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ERR-AUTH-005 / ERR-TASK-005 / ERR-TASK-006</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ERR-SYS-001 / ERR-SYS-999</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ERR-INPUT-001 / ERR-USR-001</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ERR-INPUT-001 / ERR-AUTH-002</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ERR-TASK-004 / ERR-AUTH-005 / ERR-AUTH-001</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ERR-TASK-001 等 / ERR-USR-002 / ERR-AUTH-001</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ERR-TASK-001 等 / ERR-TASK-004 / ERR-TASK-005 / ERR-AUTH-001</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ERR-TASK-004 / ERR-TASK-006 / ERR-AUTH-001</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -1616,7 +1462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD58F037-A34A-1A47-91B0-F666D63387F7}">
   <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
@@ -1626,48 +1472,48 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17">
       <c r="A1" s="8" t="s">
-        <v>0</v>
+        <v>307</v>
       </c>
       <c r="B1" s="9"/>
     </row>
     <row r="2" spans="1:2" ht="15">
       <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="30">
       <c r="A3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>3</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15">
       <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>5</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>8</v>
+        <v>290</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15">
       <c r="A6" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1681,7 +1527,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1695,7 +1541,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17">
       <c r="A1" s="8" t="s">
-        <v>288</v>
+        <v>159</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -1706,347 +1552,232 @@
     </row>
     <row r="2" spans="1:7" ht="15">
       <c r="A2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="30">
+      <c r="A3" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>290</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="15">
-      <c r="A3" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="B3" s="3" t="s">
-        <v>293</v>
+        <v>164</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>294</v>
+        <v>259</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>295</v>
+        <v>260</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>296</v>
+        <v>315</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>297</v>
+        <v>261</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="15">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30">
       <c r="A4" s="2" t="s">
-        <v>299</v>
+        <v>165</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>300</v>
+        <v>166</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>110</v>
+        <v>263</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>107</v>
+        <v>174</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>109</v>
+        <v>316</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>301</v>
+        <v>264</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="15">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="30">
       <c r="A5" s="2" t="s">
-        <v>303</v>
+        <v>266</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>304</v>
+        <v>267</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>83</v>
+        <v>268</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>106</v>
+        <v>311</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>305</v>
+        <v>269</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>306</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="30">
       <c r="A6" s="2" t="s">
-        <v>307</v>
+        <v>167</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>308</v>
+        <v>168</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>310</v>
+        <v>90</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>311</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>312</v>
+        <v>271</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="15">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="30">
       <c r="A7" s="2" t="s">
-        <v>314</v>
+        <v>169</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>315</v>
+        <v>170</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>316</v>
+        <v>272</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="F7" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="30">
+      <c r="A8" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F8" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="45">
+      <c r="A9" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="45">
-      <c r="A8" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="30">
-      <c r="A9" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>331</v>
-      </c>
       <c r="F9" s="3" t="s">
-        <v>332</v>
+        <v>281</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>185</v>
+        <v>282</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="30">
       <c r="A10" s="2" t="s">
-        <v>333</v>
+        <v>177</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>334</v>
+        <v>178</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>335</v>
+        <v>272</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>336</v>
+        <v>273</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>337</v>
+        <v>320</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>338</v>
+        <v>283</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11" spans="1:7" ht="30">
       <c r="A11" s="2" t="s">
-        <v>339</v>
+        <v>285</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>340</v>
+        <v>286</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>329</v>
+        <v>268</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>330</v>
+        <v>90</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>341</v>
+        <v>311</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>342</v>
+        <v>271</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="30">
-      <c r="A12" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="30">
-      <c r="A13" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="15">
-      <c r="A14" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="15">
-      <c r="A15" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="30">
-      <c r="A16" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>121</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -2069,56 +1800,56 @@
   <sheetData>
     <row r="1" spans="1:2" ht="17">
       <c r="A1" s="8" t="s">
-        <v>369</v>
+        <v>179</v>
       </c>
       <c r="B1" s="9"/>
     </row>
     <row r="2" spans="1:2" ht="15">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15">
       <c r="A3" s="2" t="s">
-        <v>370</v>
+        <v>180</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>371</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15">
       <c r="A4" s="2" t="s">
-        <v>372</v>
+        <v>181</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>373</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15">
       <c r="A5" s="2" t="s">
-        <v>374</v>
+        <v>183</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>375</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="30">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15">
       <c r="A7" s="2" t="s">
-        <v>377</v>
+        <v>185</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>378</v>
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -2133,18 +1864,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="83.83203125" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="30" customWidth="1"/>
-    <col min="5" max="5" width="18" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="53.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="40.83203125" customWidth="1"/>
+    <col min="5" max="5" width="22" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17">
       <c r="A1" s="8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -2153,95 +1884,95 @@
     </row>
     <row r="2" spans="1:5" ht="15">
       <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="30">
       <c r="A3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>19</v>
-      </c>
       <c r="D3" s="3" t="s">
-        <v>20</v>
+        <v>186</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" spans="1:5" ht="30">
       <c r="A4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:5" ht="30">
+      <c r="A5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B5" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="30">
+      <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="B6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:5" ht="15">
-      <c r="A5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15">
-      <c r="A6" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>32</v>
-      </c>
       <c r="D6" s="3" t="s">
-        <v>33</v>
+        <v>192</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:5" ht="15">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>36</v>
+        <v>27</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="E7" s="3"/>
     </row>
@@ -2269,7 +2000,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17">
       <c r="A1" s="8" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -2279,151 +2010,151 @@
     </row>
     <row r="2" spans="1:6" ht="15">
       <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6" ht="15">
       <c r="A4" s="2" t="s">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6" ht="15">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>52</v>
-      </c>
       <c r="D5" s="3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" ht="15">
       <c r="A6" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="30">
       <c r="A7" s="2" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>63</v>
+        <v>193</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15">
       <c r="A8" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6" ht="15">
       <c r="A9" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>72</v>
+        <v>194</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="F9" s="3"/>
     </row>
@@ -2439,18 +2170,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:E8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="28.6640625" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
-    <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="1" max="1" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="32.1640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="17">
       <c r="A1" s="8" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -2459,108 +2190,108 @@
     </row>
     <row r="2" spans="1:5" ht="15">
       <c r="A2" s="1" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15">
       <c r="A3" s="4" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:5" ht="15">
+    <row r="4" spans="1:5" ht="30">
       <c r="A4" s="4" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>83</v>
+        <v>195</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>84</v>
+        <v>196</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:5" ht="15">
       <c r="A5" s="4" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>88</v>
+        <v>197</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>89</v>
+        <v>76</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" spans="1:5" ht="15">
       <c r="A6" s="4" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>92</v>
+        <v>198</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7" spans="1:5" ht="15">
       <c r="A7" s="4" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="1:5" ht="15">
+      <c r="A8" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="E7" s="3"/>
-    </row>
-    <row r="8" spans="1:5" ht="30">
-      <c r="A8" s="5" t="s">
-        <v>96</v>
-      </c>
       <c r="B8" s="3" t="s">
-        <v>97</v>
+        <v>82</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>98</v>
+        <v>199</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="E8" s="3"/>
     </row>
@@ -2575,7 +2306,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2589,7 +2320,7 @@
   <sheetData>
     <row r="1" spans="1:7" ht="17">
       <c r="A1" s="8" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -2600,725 +2331,379 @@
     </row>
     <row r="2" spans="1:7" ht="15">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15">
       <c r="A3" s="4" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>106</v>
+        <v>291</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>108</v>
+        <v>200</v>
       </c>
       <c r="G3" s="3"/>
     </row>
-    <row r="4" spans="1:7" ht="30">
+    <row r="4" spans="1:7" ht="15">
       <c r="A4" s="4" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>109</v>
+        <v>292</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>111</v>
+        <v>201</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>379</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="15">
       <c r="A5" s="4" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>112</v>
+        <v>294</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G5" s="3"/>
+        <v>93</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="6" spans="1:7" ht="15">
       <c r="A6" s="4" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>115</v>
+        <v>295</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="G6" s="3"/>
-    </row>
-    <row r="7" spans="1:7" ht="15">
+        <v>93</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="45">
       <c r="A7" s="4" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>118</v>
+        <v>304</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>117</v>
+        <v>205</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>119</v>
+        <v>206</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G7" s="3"/>
+        <v>97</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="8" spans="1:7" ht="15">
       <c r="A8" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>123</v>
+        <v>305</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>124</v>
+        <v>99</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="15">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="30">
       <c r="A9" s="2" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>128</v>
+        <v>306</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>122</v>
+        <v>98</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>129</v>
+        <v>103</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>130</v>
+        <v>104</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="G9" s="3"/>
+        <v>105</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>215</v>
+      </c>
     </row>
     <row r="10" spans="1:7" ht="15">
       <c r="A10" s="2" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>132</v>
+        <v>296</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>133</v>
+        <v>213</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>134</v>
+        <v>107</v>
       </c>
       <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:7" ht="15">
       <c r="A11" s="2" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>53</v>
+        <v>297</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:7" ht="15">
       <c r="A12" s="2" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>138</v>
+        <v>298</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>139</v>
+        <v>214</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="G12" s="3"/>
     </row>
     <row r="13" spans="1:7" ht="15">
       <c r="A13" s="2" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>141</v>
+        <v>299</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>49</v>
+        <v>104</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>143</v>
+        <v>216</v>
       </c>
       <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:7" ht="15">
       <c r="A14" s="2" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>144</v>
+        <v>300</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>145</v>
+        <v>113</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>130</v>
+        <v>96</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>146</v>
+        <v>97</v>
       </c>
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:7" ht="15">
       <c r="A15" s="2" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>147</v>
+        <v>301</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="G15" s="3"/>
     </row>
     <row r="16" spans="1:7" ht="15">
       <c r="A16" s="2" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>149</v>
+        <v>302</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>150</v>
+        <v>217</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>121</v>
+        <v>218</v>
       </c>
       <c r="G16" s="3"/>
     </row>
     <row r="17" spans="1:7" ht="15">
       <c r="A17" s="2" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>152</v>
+        <v>303</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>153</v>
+        <v>117</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>154</v>
+        <v>218</v>
       </c>
       <c r="G17" s="3"/>
     </row>
-    <row r="18" spans="1:7" ht="15">
+    <row r="18" spans="1:7" ht="30">
       <c r="A18" s="2" t="s">
-        <v>151</v>
+        <v>208</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>155</v>
+        <v>308</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>151</v>
+        <v>209</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>156</v>
+        <v>210</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="G18" s="3"/>
-    </row>
-    <row r="19" spans="1:7" ht="15">
-      <c r="A19" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G19" s="3"/>
-    </row>
-    <row r="20" spans="1:7" ht="15">
-      <c r="A20" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G20" s="3"/>
-    </row>
-    <row r="21" spans="1:7" ht="15">
-      <c r="A21" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="G21" s="3"/>
-    </row>
-    <row r="22" spans="1:7" ht="15">
-      <c r="A22" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="G22" s="3"/>
-    </row>
-    <row r="23" spans="1:7" ht="15">
-      <c r="A23" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G23" s="3"/>
-    </row>
-    <row r="24" spans="1:7" ht="15">
-      <c r="A24" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="G24" s="3"/>
-    </row>
-    <row r="25" spans="1:7" ht="15">
-      <c r="A25" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G25" s="3"/>
-    </row>
-    <row r="26" spans="1:7" ht="15">
-      <c r="A26" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="G26" s="3"/>
-    </row>
-    <row r="27" spans="1:7" ht="15">
-      <c r="A27" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="G27" s="3"/>
-    </row>
-    <row r="28" spans="1:7" ht="15">
-      <c r="A28" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="G28" s="3"/>
-    </row>
-    <row r="29" spans="1:7" ht="15">
-      <c r="A29" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G29" s="3"/>
-    </row>
-    <row r="30" spans="1:7" ht="15">
-      <c r="A30" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="G30" s="3"/>
-    </row>
-    <row r="31" spans="1:7" ht="15">
-      <c r="A31" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="G31" s="3"/>
-    </row>
-    <row r="32" spans="1:7" ht="15">
-      <c r="A32" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="G32" s="3"/>
-    </row>
-    <row r="33" spans="1:7" ht="15">
-      <c r="A33" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="G33" s="3"/>
-    </row>
-    <row r="34" spans="1:7" ht="15">
-      <c r="A34" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="G34" s="3"/>
-    </row>
-    <row r="35" spans="1:7" ht="15">
-      <c r="A35" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="G35" s="3"/>
+        <v>211</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>212</v>
+      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A2:G18" xr:uid="{00000000-0001-0000-0400-000000000000}"/>
   <mergeCells count="1">
     <mergeCell ref="A1:G1"/>
   </mergeCells>
@@ -3334,7 +2719,7 @@
   <cols>
     <col min="1" max="1" width="16" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="3" max="3" width="53.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
     <col min="6" max="6" width="18" customWidth="1"/>
@@ -3342,7 +2727,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="17">
       <c r="A1" s="8" t="s">
-        <v>206</v>
+        <v>118</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -3352,93 +2737,93 @@
     </row>
     <row r="2" spans="1:6" ht="15">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>207</v>
+        <v>119</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>208</v>
+        <v>120</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>209</v>
+        <v>121</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="30">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="15">
       <c r="A3" s="2" t="s">
-        <v>210</v>
+        <v>122</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>63</v>
+        <v>193</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>211</v>
+        <v>123</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>212</v>
+        <v>124</v>
       </c>
       <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:6" ht="15">
       <c r="A4" s="2" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>213</v>
+        <v>125</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>214</v>
+        <v>126</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>215</v>
+        <v>127</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>212</v>
+        <v>124</v>
       </c>
       <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6" ht="15">
       <c r="A5" s="2" t="s">
-        <v>216</v>
+        <v>128</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>217</v>
+        <v>129</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>219</v>
+        <v>130</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>212</v>
+        <v>124</v>
       </c>
       <c r="F5" s="3"/>
     </row>
     <row r="6" spans="1:6" ht="15">
       <c r="A6" s="2" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>220</v>
+        <v>131</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>221</v>
+        <v>132</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>212</v>
+        <v>124</v>
       </c>
       <c r="F6" s="3"/>
     </row>
@@ -3454,19 +2839,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:F10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="61.1640625" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="32" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="1" max="1" width="40.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="56" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="45.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17">
       <c r="A1" s="8" t="s">
-        <v>222</v>
+        <v>133</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -3476,172 +2861,178 @@
     </row>
     <row r="2" spans="1:6" ht="15">
       <c r="A2" s="1" t="s">
-        <v>223</v>
+        <v>134</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>224</v>
+        <v>135</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>225</v>
+        <v>136</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>209</v>
+        <v>121</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15">
       <c r="A3" s="6" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>227</v>
+        <v>309</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="F3" s="3"/>
+        <v>124</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="4" spans="1:6" ht="15">
       <c r="A4" s="6" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>107</v>
+        <v>40</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>109</v>
+        <v>310</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>212</v>
+        <v>124</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="30">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15">
       <c r="A5" s="6" t="s">
-        <v>232</v>
+        <v>202</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>233</v>
+        <v>293</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="F5" s="3"/>
+        <v>124</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="15">
       <c r="A6" s="6" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>130</v>
+        <v>90</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>236</v>
+        <v>311</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="F6" s="3"/>
+        <v>124</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="15">
       <c r="A7" s="6" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>239</v>
+        <v>312</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>240</v>
+        <v>138</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>212</v>
+        <v>124</v>
       </c>
       <c r="F7" s="3"/>
     </row>
     <row r="8" spans="1:6" ht="15">
       <c r="A8" s="7" t="s">
-        <v>241</v>
+        <v>139</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>175</v>
+        <v>100</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>173</v>
+        <v>305</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>244</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="F8" s="3"/>
     </row>
     <row r="9" spans="1:6" ht="15">
       <c r="A9" s="7" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>175</v>
+        <v>96</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>201</v>
+        <v>313</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="F9" s="3"/>
+        <v>124</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>235</v>
+      </c>
     </row>
     <row r="10" spans="1:6" ht="15">
       <c r="A10" s="7" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>175</v>
+        <v>115</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>204</v>
+        <v>314</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>243</v>
+        <v>140</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -3656,19 +3047,19 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="60.5" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="30" customWidth="1"/>
-    <col min="3" max="3" width="22" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="20" customWidth="1"/>
-    <col min="6" max="6" width="22" customWidth="1"/>
+    <col min="1" max="1" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="59.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="34.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17">
       <c r="A1" s="8" t="s">
-        <v>250</v>
+        <v>141</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -3678,117 +3069,123 @@
     </row>
     <row r="2" spans="1:6" ht="15">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>209</v>
+        <v>121</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>251</v>
+        <v>142</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="30">
       <c r="A3" s="2" t="s">
-        <v>252</v>
+        <v>143</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>253</v>
+        <v>239</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>72</v>
+        <v>194</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>254</v>
+        <v>240</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>255</v>
+        <v>241</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="30">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="15">
       <c r="A4" s="2" t="s">
-        <v>257</v>
+        <v>144</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>259</v>
+        <v>240</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>261</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15">
       <c r="A5" s="2" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>263</v>
+        <v>145</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>212</v>
+        <v>246</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="F5" s="3"/>
+        <v>247</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="6" spans="1:6" ht="15">
       <c r="A6" s="2" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>265</v>
+        <v>249</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>266</v>
+        <v>199</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="F6" s="3"/>
+        <v>241</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>251</v>
+      </c>
     </row>
     <row r="7" spans="1:6" ht="15">
       <c r="A7" s="2" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>109</v>
+        <v>228</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>212</v>
+        <v>90</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="F7" s="3"/>
+        <v>247</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>253</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3813,7 +3210,7 @@
   <sheetData>
     <row r="1" spans="1:5" ht="17">
       <c r="A1" s="8" t="s">
-        <v>270</v>
+        <v>146</v>
       </c>
       <c r="B1" s="9"/>
       <c r="C1" s="9"/>
@@ -3822,80 +3219,80 @@
     </row>
     <row r="2" spans="1:5" ht="15">
       <c r="A2" s="1" t="s">
-        <v>271</v>
+        <v>147</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>272</v>
+        <v>148</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>273</v>
+        <v>149</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="30">
       <c r="A3" s="2" t="s">
-        <v>274</v>
+        <v>150</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>275</v>
+        <v>151</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>276</v>
+        <v>152</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>277</v>
+        <v>153</v>
       </c>
       <c r="E3" s="3"/>
     </row>
-    <row r="4" spans="1:5" ht="30">
+    <row r="4" spans="1:5" ht="60">
       <c r="A4" s="2" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>279</v>
+        <v>255</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>280</v>
+        <v>256</v>
       </c>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:5" ht="30">
+    <row r="5" spans="1:5" ht="45">
       <c r="A5" s="2" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>281</v>
+        <v>154</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>282</v>
+        <v>257</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>283</v>
+        <v>155</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="15">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="30">
       <c r="A6" s="2" t="s">
-        <v>113</v>
+        <v>92</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>285</v>
+        <v>157</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>286</v>
+        <v>258</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>287</v>
+        <v>158</v>
       </c>
       <c r="E6" s="3"/>
     </row>
